--- a/Design-Files/ASCII-v1.2/Deliverables/BOM/JLCPCB-BOM-ASCII-v1.2.xlsx
+++ b/Design-Files/ASCII-v1.2/Deliverables/BOM/JLCPCB-BOM-ASCII-v1.2.xlsx
@@ -581,7 +581,7 @@
     <t>10K</t>
   </si>
   <si>
-    <t>R11, R12, R14, R15, R16, R27, R29</t>
+    <t>R11, R12, R14, R15, R16, R27, R29,R30</t>
   </si>
   <si>
     <t>C190095</t>
@@ -812,7 +812,7 @@
     <t>C1337508</t>
   </si>
   <si>
-    <t>ESP32-WROOM-32</t>
+    <t>ESP32-WROOM-32E-N4</t>
   </si>
   <si>
     <t>U14</t>
@@ -870,7 +870,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -882,13 +882,6 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1478,148 +1471,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1634,46 +1627,46 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3073,7 +3066,7 @@
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="13" t="s">
+      <c r="A77" t="s">
         <v>261</v>
       </c>
       <c r="B77" s="14" t="s">

--- a/Design-Files/ASCII-v1.2/Deliverables/BOM/JLCPCB-BOM-ASCII-v1.2.xlsx
+++ b/Design-Files/ASCII-v1.2/Deliverables/BOM/JLCPCB-BOM-ASCII-v1.2.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="273">
   <si>
     <t>Comment</t>
   </si>
@@ -398,22 +398,10 @@
     <t>C160404</t>
   </si>
   <si>
-    <t>8.2nH</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>YSPIT0550A-8R2M</t>
-  </si>
-  <si>
-    <t>C18236292</t>
-  </si>
-  <si>
     <t>2.2uH</t>
   </si>
   <si>
-    <t>L2</t>
+    <t>L1,L2</t>
   </si>
   <si>
     <t>PSPMAA0503-2R2M-ANP</t>
@@ -1994,7 +1982,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="18.7142857142857" style="1" customWidth="1"/>
@@ -2573,7 +2561,7 @@
       <c r="C41" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="7" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2585,23 +2573,23 @@
         <v>144</v>
       </c>
       <c r="C42" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>145</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B43" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="C43" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="C43" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="14" t="s">
         <v>149</v>
       </c>
     </row>
@@ -2627,105 +2615,105 @@
         <v>155</v>
       </c>
       <c r="C45" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D45" s="14" t="s">
         <v>156</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="C46" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D46" s="14" t="s">
         <v>159</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B47" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="C47" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D47" s="14" t="s">
         <v>162</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B48" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="C48" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D48" s="14" t="s">
         <v>165</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="C49" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D49" s="14" t="s">
         <v>168</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B50" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="C50" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D50" s="14" t="s">
         <v>171</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B51" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="C51" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" s="14" t="s">
         <v>174</v>
-      </c>
-      <c r="C51" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B52" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="C52" s="14" t="s">
         <v>177</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>156</v>
       </c>
       <c r="D52" s="14" t="s">
         <v>178</v>
@@ -2739,175 +2727,175 @@
         <v>180</v>
       </c>
       <c r="C53" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D53" s="14" t="s">
         <v>181</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B54" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="C54" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D54" s="14" t="s">
         <v>184</v>
-      </c>
-      <c r="C54" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B55" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="C55" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D55" s="14" t="s">
         <v>187</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B56" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="C56" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D56" s="14" t="s">
         <v>190</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="B57" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="C57" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D57" s="14" t="s">
         <v>193</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B58" s="14" t="s">
         <v>195</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>196</v>
       </c>
       <c r="C58" s="14" t="s">
         <v>152</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B59" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="C59" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D59" s="14" t="s">
         <v>199</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="B60" s="14" t="s">
         <v>201</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>202</v>
       </c>
       <c r="C60" s="14" t="s">
         <v>152</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B61" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="C61" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D61" s="14" t="s">
         <v>205</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="B62" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="C62" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D62" s="14" t="s">
         <v>208</v>
-      </c>
-      <c r="C62" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B63" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="B63" s="14" t="s">
+      <c r="C63" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D63" s="14" t="s">
         <v>211</v>
-      </c>
-      <c r="C63" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B64" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="B64" s="14" t="s">
+      <c r="C64" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="D64" s="14" t="s">
         <v>214</v>
-      </c>
-      <c r="C64" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="B65" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="C65" s="14" t="s">
         <v>217</v>
-      </c>
-      <c r="C65" s="14" t="s">
-        <v>216</v>
       </c>
       <c r="D65" s="14" t="s">
         <v>218</v>
@@ -2951,21 +2939,21 @@
       <c r="C68" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="D68" s="14" t="s">
-        <v>230</v>
-      </c>
+      <c r="D68" s="7"/>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B69" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="C69" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="D69" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="D69" s="7"/>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="13" t="s">
@@ -2975,23 +2963,23 @@
         <v>235</v>
       </c>
       <c r="C70" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D70" s="14" t="s">
         <v>236</v>
-      </c>
-      <c r="D70" s="14" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B71" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="B71" s="14" t="s">
+      <c r="C71" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="C71" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="D71" s="14" t="s">
+      <c r="D71" s="7" t="s">
         <v>240</v>
       </c>
     </row>
@@ -3005,7 +2993,7 @@
       <c r="C72" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="D72" s="14" t="s">
         <v>244</v>
       </c>
     </row>
@@ -3047,12 +3035,12 @@
       <c r="C75" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="D75" s="14" t="s">
+      <c r="D75" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="13" t="s">
+      <c r="A76" t="s">
         <v>257</v>
       </c>
       <c r="B76" s="14" t="s">
@@ -3066,7 +3054,7 @@
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" t="s">
+      <c r="A77" s="13" t="s">
         <v>261</v>
       </c>
       <c r="B77" s="14" t="s">
@@ -3075,7 +3063,7 @@
       <c r="C77" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D77" s="14" t="s">
         <v>264</v>
       </c>
     </row>
@@ -3094,31 +3082,17 @@
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="B79" s="14" t="s">
+      <c r="B79" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="D79" s="14" t="s">
+      <c r="D79" s="17" t="s">
         <v>272</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="16" t="s">
-        <v>273</v>
-      </c>
-      <c r="B80" s="17" t="s">
-        <v>274</v>
-      </c>
-      <c r="C80" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="D80" s="17" t="s">
-        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/Design-Files/ASCII-v1.2/Deliverables/BOM/JLCPCB-BOM-ASCII-v1.2.xlsx
+++ b/Design-Files/ASCII-v1.2/Deliverables/BOM/JLCPCB-BOM-ASCII-v1.2.xlsx
@@ -599,7 +599,7 @@
     <t>R18</t>
   </si>
   <si>
-    <t>C474536</t>
+    <t>C185370</t>
   </si>
   <si>
     <t>75K</t>
